--- a/dist/assets/PediDoses-Ampoules.xlsx
+++ b/dist/assets/PediDoses-Ampoules.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ampoules" sheetId="1" r:id="Rf57250932de44da1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode d’emploi" sheetId="2" r:id="R8f02eb54d57f454b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ampoules" sheetId="1" r:id="Rd80d76bd82294721"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode d’emploi" sheetId="2" r:id="Raf2bd21fd0034aa6"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -14,10 +14,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="1">
+  <x:numFmts count="2">
     <x:numFmt numFmtId="200" formatCode="0.00##########"/>
+    <x:numFmt numFmtId="201" formatCode="0.00"/>
   </x:numFmts>
-  <x:fonts count="4">
+  <x:fonts count="5">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -37,8 +38,12 @@
       <x:sz val="11"/>
       <x:name val="Arial"/>
     </x:font>
+    <x:font>
+      <x:sz val="10"/>
+      <x:name val="Arial"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="5">
+  <x:fills count="7">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -60,6 +65,16 @@
         <x:fgColor rgb="FFF2F4F6"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF2CC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE7E6E6"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="2">
     <x:border/>
@@ -72,7 +87,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="16">
+  <x:cellXfs count="23">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -117,6 +132,25 @@
     <x:xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="4" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="4" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -124,7 +158,7 @@
   <x:dxfs count="1">
     <x:dxf>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF1D6"/>
         </x:patternFill>
       </x:fill>
@@ -134,8 +168,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="AmpoulesPediDoses" displayName="AmpoulesPediDoses" ref="A1:L64" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:L64"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="AmpoulesPediDoses" displayName="AmpoulesPediDoses" ref="A1:L67" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:L67"/>
   <x:tableColumns count="12">
     <x:tableColumn id="1" name="Identifiant"/>
     <x:tableColumn id="2" name="Médicament"/>
@@ -516,23 +550,25 @@
       <x:c r="C5" s="3" t="str">
         <x:v>Chlorure de calcium</x:v>
       </x:c>
-      <x:c r="D5" s="7"/>
-      <x:c r="E5" s="7"/>
+      <x:c r="D5" s="7" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E5" s="7" t="n">
+        <x:v>1000</x:v>
+      </x:c>
       <x:c r="F5" s="6" t="str">
         <x:v>mg</x:v>
       </x:c>
-      <x:c r="G5" s="7" t="n">
-        <x:v>100</x:v>
-      </x:c>
+      <x:c r="G5" s="7"/>
       <x:c r="H5" s="9" t="n">
         <x:f>IF(AND(ISNUMBER(D5),D5&gt;0,ISNUMBER(E5),E5&gt;0),E5/D5,IF(ISNUMBER(G5),G5,""))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="I5" s="3" t="str">
-        <x:v>chlorure de calcium — expression de dose à confirmer</x:v>
+        <x:v>chlorure de calcium</x:v>
       </x:c>
       <x:c r="J5" s="3" t="str">
-        <x:v>à confirmer</x:v>
+        <x:v>confirmé</x:v>
       </x:c>
       <x:c r="K5" s="3" t="str"/>
       <x:c r="L5" s="3" t="str">
@@ -670,10 +706,12 @@
         <x:v>Amoxicilline / acide clavulanique</x:v>
       </x:c>
       <x:c r="C10" s="3" t="str">
-        <x:v>Poudre pour solution injectable</x:v>
+        <x:v>Poudre pour solution injectable 500 mg/50 mg</x:v>
       </x:c>
       <x:c r="D10" s="7"/>
-      <x:c r="E10" s="7"/>
+      <x:c r="E10" s="7" t="n">
+        <x:v>500</x:v>
+      </x:c>
       <x:c r="F10" s="6" t="str">
         <x:v>mg</x:v>
       </x:c>
@@ -682,14 +720,12 @@
         <x:f>IF(AND(ISNUMBER(D10),D10&gt;0,ISNUMBER(E10),E10&gt;0),E10/D10,IF(ISNUMBER(G10),G10,""))</x:f>
       </x:c>
       <x:c r="I10" s="3" t="str">
-        <x:v>amoxicilline</x:v>
+        <x:v>amoxicilline (500 mg / 50 mg d’acide clavulanique)</x:v>
       </x:c>
       <x:c r="J10" s="3" t="str">
-        <x:v>à confirmer</x:v>
-      </x:c>
-      <x:c r="K10" s="3" t="str">
-        <x:v>Renseigner le dosage et le rapport amoxicilline/acide clavulanique.</x:v>
-      </x:c>
+        <x:v>confirmé</x:v>
+      </x:c>
+      <x:c r="K10" s="3" t="str"/>
       <x:c r="L10" s="3" t="str">
         <x:v>Tableau Prescription / Ampoules et décisions locales de la conversation</x:v>
       </x:c>
@@ -871,28 +907,29 @@
         <x:v>Sulfate de magnésium</x:v>
       </x:c>
       <x:c r="C16" s="3" t="str">
-        <x:v>Sulfate magnéisum</x:v>
+        <x:v>Sulfate de magnésium 15 %</x:v>
       </x:c>
       <x:c r="D16" s="7" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="E16" s="7"/>
+      <x:c r="E16" s="7" t="n">
+        <x:v>1.5</x:v>
+      </x:c>
       <x:c r="F16" s="6" t="str">
         <x:v>g</x:v>
       </x:c>
       <x:c r="G16" s="7"/>
-      <x:c r="H16" s="9" t="str">
+      <x:c r="H16" s="9" t="n">
         <x:f>IF(AND(ISNUMBER(D16),D16&gt;0,ISNUMBER(E16),E16&gt;0),E16/D16,IF(ISNUMBER(G16),G16,""))</x:f>
+        <x:v>0.15</x:v>
       </x:c>
       <x:c r="I16" s="3" t="str">
         <x:v>sulfate de magnésium</x:v>
       </x:c>
       <x:c r="J16" s="3" t="str">
-        <x:v>à confirmer</x:v>
-      </x:c>
-      <x:c r="K16" s="3" t="str">
-        <x:v>À trancher : 0,15 g par mL (= 1,5 g/10 mL à 15 %) ou 0,15 g par ampoule de 10 mL. Quantité volontairement vide.</x:v>
-      </x:c>
+        <x:v>confirmé</x:v>
+      </x:c>
+      <x:c r="K16" s="3" t="str"/>
       <x:c r="L16" s="3" t="str">
         <x:v>https://base-donnees-publique.medicaments.gouv.fr/medicament/61106121/extrait</x:v>
       </x:c>
@@ -902,7 +939,7 @@
         <x:v>triphosadenine</x:v>
       </x:c>
       <x:c r="B17" s="3" t="str">
-        <x:v>Triphosadénine</x:v>
+        <x:v>Triphosadénine — 1re dose</x:v>
       </x:c>
       <x:c r="C17" s="3" t="str">
         <x:v>Striadyne</x:v>
@@ -922,7 +959,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="I17" s="3" t="str">
-        <x:v>Triphosadénine</x:v>
+        <x:v>Triphosadénine — 1re dose</x:v>
       </x:c>
       <x:c r="J17" s="3" t="str">
         <x:v>à confirmer</x:v>
@@ -1135,7 +1172,7 @@
         <x:v>Morphine (titration)</x:v>
       </x:c>
       <x:c r="J23" s="3" t="str">
-        <x:v>à confirmer</x:v>
+        <x:v>confirmé</x:v>
       </x:c>
       <x:c r="K23" s="3" t="str"/>
       <x:c r="L23" s="3" t="str">
@@ -1152,14 +1189,16 @@
       <x:c r="C24" s="3" t="str">
         <x:v>Propofol</x:v>
       </x:c>
-      <x:c r="D24" s="7"/>
-      <x:c r="E24" s="7"/>
+      <x:c r="D24" s="7" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="E24" s="7" t="n">
+        <x:v>200</x:v>
+      </x:c>
       <x:c r="F24" s="6" t="str">
         <x:v>mg</x:v>
       </x:c>
-      <x:c r="G24" s="7" t="n">
-        <x:v>10</x:v>
-      </x:c>
+      <x:c r="G24" s="7"/>
       <x:c r="H24" s="9" t="n">
         <x:f>IF(AND(ISNUMBER(D24),D24&gt;0,ISNUMBER(E24),E24&gt;0),E24/D24,IF(ISNUMBER(G24),G24,""))</x:f>
         <x:v>10</x:v>
@@ -1168,7 +1207,7 @@
         <x:v>Propofol</x:v>
       </x:c>
       <x:c r="J24" s="3" t="str">
-        <x:v>à confirmer</x:v>
+        <x:v>confirmé</x:v>
       </x:c>
       <x:c r="K24" s="3" t="str"/>
       <x:c r="L24" s="3" t="str">
@@ -1180,28 +1219,30 @@
         <x:v>suxamethonium</x:v>
       </x:c>
       <x:c r="B25" s="3" t="str">
-        <x:v>Suxaméthonium</x:v>
+        <x:v>Suxaméthonium (Célocurine)</x:v>
       </x:c>
       <x:c r="C25" s="3" t="str">
-        <x:v>Celocurine</x:v>
-      </x:c>
-      <x:c r="D25" s="7"/>
-      <x:c r="E25" s="7"/>
+        <x:v>Célocurine</x:v>
+      </x:c>
+      <x:c r="D25" s="7" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E25" s="7" t="n">
+        <x:v>100</x:v>
+      </x:c>
       <x:c r="F25" s="6" t="str">
         <x:v>mg</x:v>
       </x:c>
-      <x:c r="G25" s="7" t="n">
-        <x:v>50</x:v>
-      </x:c>
+      <x:c r="G25" s="7"/>
       <x:c r="H25" s="9" t="n">
         <x:f>IF(AND(ISNUMBER(D25),D25&gt;0,ISNUMBER(E25),E25&gt;0),E25/D25,IF(ISNUMBER(G25),G25,""))</x:f>
         <x:v>50</x:v>
       </x:c>
       <x:c r="I25" s="3" t="str">
-        <x:v>Suxaméthonium</x:v>
+        <x:v>Suxaméthonium (Célocurine)</x:v>
       </x:c>
       <x:c r="J25" s="3" t="str">
-        <x:v>à confirmer</x:v>
+        <x:v>confirmé</x:v>
       </x:c>
       <x:c r="K25" s="3" t="str"/>
       <x:c r="L25" s="3" t="str">
@@ -1251,7 +1292,7 @@
         <x:v>Clonazépam</x:v>
       </x:c>
       <x:c r="C27" s="3" t="str">
-        <x:v>Rivotril</x:v>
+        <x:v>Clonazépam — ampoule seule</x:v>
       </x:c>
       <x:c r="D27" s="7" t="n">
         <x:v>1</x:v>
@@ -1271,7 +1312,7 @@
         <x:v>Clonazépam</x:v>
       </x:c>
       <x:c r="J27" s="3" t="str">
-        <x:v>à confirmer</x:v>
+        <x:v>confirmé</x:v>
       </x:c>
       <x:c r="K27" s="3" t="str"/>
       <x:c r="L27" s="3" t="str">
@@ -1395,14 +1436,16 @@
       <x:c r="C31" s="3" t="str">
         <x:v>Keppra</x:v>
       </x:c>
-      <x:c r="D31" s="7"/>
-      <x:c r="E31" s="7"/>
+      <x:c r="D31" s="7" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="E31" s="7" t="n">
+        <x:v>500</x:v>
+      </x:c>
       <x:c r="F31" s="6" t="str">
         <x:v>mg</x:v>
       </x:c>
-      <x:c r="G31" s="7" t="n">
-        <x:v>100</x:v>
-      </x:c>
+      <x:c r="G31" s="7"/>
       <x:c r="H31" s="9" t="n">
         <x:f>IF(AND(ISNUMBER(D31),D31&gt;0,ISNUMBER(E31),E31&gt;0),E31/D31,IF(ISNUMBER(G31),G31,""))</x:f>
         <x:v>100</x:v>
@@ -1411,7 +1454,7 @@
         <x:v>Lévétiracétam</x:v>
       </x:c>
       <x:c r="J31" s="3" t="str">
-        <x:v>à confirmer</x:v>
+        <x:v>confirmé</x:v>
       </x:c>
       <x:c r="K31" s="3" t="str"/>
       <x:c r="L31" s="3" t="str">
@@ -1479,11 +1522,9 @@
         <x:v>chlorure de sodium</x:v>
       </x:c>
       <x:c r="J33" s="3" t="str">
-        <x:v>à confirmer</x:v>
-      </x:c>
-      <x:c r="K33" s="3" t="str">
-        <x:v>Préparation fournie par la pharmacie ; aucune dilution à réaliser.</x:v>
-      </x:c>
+        <x:v>confirmé</x:v>
+      </x:c>
+      <x:c r="K33" s="3" t="str"/>
       <x:c r="L33" s="3" t="str">
         <x:v>Tableau Prescription / Ampoules et décisions locales de la conversation</x:v>
       </x:c>
@@ -1549,7 +1590,7 @@
         <x:v>citrate de caféine</x:v>
       </x:c>
       <x:c r="J35" s="3" t="str">
-        <x:v>à confirmer</x:v>
+        <x:v>confirmé</x:v>
       </x:c>
       <x:c r="K35" s="3" t="str"/>
       <x:c r="L35" s="3" t="str">
@@ -1566,14 +1607,16 @@
       <x:c r="C36" s="3" t="str">
         <x:v>Flumazenil</x:v>
       </x:c>
-      <x:c r="D36" s="7"/>
-      <x:c r="E36" s="7"/>
+      <x:c r="D36" s="7" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E36" s="7" t="n">
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="F36" s="6" t="str">
         <x:v>mg</x:v>
       </x:c>
-      <x:c r="G36" s="7" t="n">
-        <x:v>0.1</x:v>
-      </x:c>
+      <x:c r="G36" s="7"/>
       <x:c r="H36" s="9" t="n">
         <x:f>IF(AND(ISNUMBER(D36),D36&gt;0,ISNUMBER(E36),E36&gt;0),E36/D36,IF(ISNUMBER(G36),G36,""))</x:f>
         <x:v>0.1</x:v>
@@ -1582,7 +1625,7 @@
         <x:v>Flumazénil</x:v>
       </x:c>
       <x:c r="J36" s="3" t="str">
-        <x:v>à confirmer</x:v>
+        <x:v>confirmé</x:v>
       </x:c>
       <x:c r="K36" s="3" t="str"/>
       <x:c r="L36" s="3" t="str">
@@ -1599,14 +1642,16 @@
       <x:c r="C37" s="3" t="str">
         <x:v>Bridion</x:v>
       </x:c>
-      <x:c r="D37" s="7"/>
-      <x:c r="E37" s="7"/>
+      <x:c r="D37" s="7" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E37" s="7" t="n">
+        <x:v>200</x:v>
+      </x:c>
       <x:c r="F37" s="6" t="str">
         <x:v>mg</x:v>
       </x:c>
-      <x:c r="G37" s="7" t="n">
-        <x:v>100</x:v>
-      </x:c>
+      <x:c r="G37" s="7"/>
       <x:c r="H37" s="9" t="n">
         <x:f>IF(AND(ISNUMBER(D37),D37&gt;0,ISNUMBER(E37),E37&gt;0),E37/D37,IF(ISNUMBER(G37),G37,""))</x:f>
         <x:v>100</x:v>
@@ -1615,7 +1660,7 @@
         <x:v>Sugammadex</x:v>
       </x:c>
       <x:c r="J37" s="3" t="str">
-        <x:v>à confirmer</x:v>
+        <x:v>confirmé</x:v>
       </x:c>
       <x:c r="K37" s="3" t="str"/>
       <x:c r="L37" s="3" t="str">
@@ -1648,7 +1693,7 @@
         <x:v>glucose</x:v>
       </x:c>
       <x:c r="J38" s="3" t="str">
-        <x:v>à confirmer</x:v>
+        <x:v>confirmé</x:v>
       </x:c>
       <x:c r="K38" s="3" t="str"/>
       <x:c r="L38" s="3" t="str">
@@ -1665,14 +1710,16 @@
       <x:c r="C39" s="3" t="str">
         <x:v>Naloxone</x:v>
       </x:c>
-      <x:c r="D39" s="7"/>
-      <x:c r="E39" s="7"/>
+      <x:c r="D39" s="7" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E39" s="7" t="n">
+        <x:v>0.4</x:v>
+      </x:c>
       <x:c r="F39" s="6" t="str">
         <x:v>mg</x:v>
       </x:c>
-      <x:c r="G39" s="7" t="n">
-        <x:v>0.4</x:v>
-      </x:c>
+      <x:c r="G39" s="7"/>
       <x:c r="H39" s="9" t="n">
         <x:f>IF(AND(ISNUMBER(D39),D39&gt;0,ISNUMBER(E39),E39&gt;0),E39/D39,IF(ISNUMBER(G39),G39,""))</x:f>
         <x:v>0.4</x:v>
@@ -1681,7 +1728,7 @@
         <x:v>Naloxone</x:v>
       </x:c>
       <x:c r="J39" s="3" t="str">
-        <x:v>à confirmer</x:v>
+        <x:v>confirmé</x:v>
       </x:c>
       <x:c r="K39" s="3" t="str"/>
       <x:c r="L39" s="3" t="str">
@@ -1823,7 +1870,9 @@
       <x:c r="J43" s="3" t="str">
         <x:v>à confirmer</x:v>
       </x:c>
-      <x:c r="K43" s="3" t="str"/>
+      <x:c r="K43" s="3" t="str">
+        <x:v>Confirmer le conditionnement disponible ; la cible de préparation est 1 mg/mL.</x:v>
+      </x:c>
       <x:c r="L43" s="3" t="str">
         <x:v>Tableau Prescription / Ampoules et décisions locales de la conversation</x:v>
       </x:c>
@@ -1836,7 +1885,7 @@
         <x:v>Clonazépam (IVSE)</x:v>
       </x:c>
       <x:c r="C44" s="3" t="str">
-        <x:v>Rivotril</x:v>
+        <x:v>Clonazépam — ampoule seule</x:v>
       </x:c>
       <x:c r="D44" s="7" t="n">
         <x:v>1</x:v>
@@ -1856,7 +1905,7 @@
         <x:v>Clonazépam</x:v>
       </x:c>
       <x:c r="J44" s="3" t="str">
-        <x:v>à confirmer</x:v>
+        <x:v>confirmé</x:v>
       </x:c>
       <x:c r="K44" s="3" t="str"/>
       <x:c r="L44" s="3" t="str">
@@ -1976,18 +2025,16 @@
         <x:v>Midazolam (IVSE)</x:v>
       </x:c>
       <x:c r="C48" s="3" t="str">
-        <x:v>Hypnovel</x:v>
-      </x:c>
-      <x:c r="D48" s="7" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="E48" s="7" t="n">
-        <x:v>50</x:v>
-      </x:c>
+        <x:v>Midazolam 5 mg/mL — deux volumes de contenant</x:v>
+      </x:c>
+      <x:c r="D48" s="7"/>
+      <x:c r="E48" s="7"/>
       <x:c r="F48" s="6" t="str">
         <x:v>mg</x:v>
       </x:c>
-      <x:c r="G48" s="7"/>
+      <x:c r="G48" s="7" t="n">
+        <x:v>5</x:v>
+      </x:c>
       <x:c r="H48" s="9" t="n">
         <x:f>IF(AND(ISNUMBER(D48),D48&gt;0,ISNUMBER(E48),E48&gt;0),E48/D48,IF(ISNUMBER(G48),G48,""))</x:f>
         <x:v>5</x:v>
@@ -1996,7 +2043,7 @@
         <x:v>Midazolam</x:v>
       </x:c>
       <x:c r="J48" s="3" t="str">
-        <x:v>à confirmer</x:v>
+        <x:v>confirmé</x:v>
       </x:c>
       <x:c r="K48" s="3" t="str"/>
       <x:c r="L48" s="3" t="str">
@@ -2031,7 +2078,7 @@
         <x:v>Morphine</x:v>
       </x:c>
       <x:c r="J49" s="3" t="str">
-        <x:v>à confirmer</x:v>
+        <x:v>confirmé</x:v>
       </x:c>
       <x:c r="K49" s="3" t="str"/>
       <x:c r="L49" s="3" t="str">
@@ -2076,7 +2123,7 @@
         <x:v>nicardipine</x:v>
       </x:c>
       <x:c r="B51" s="3" t="str">
-        <x:v>Nicardipine (IVSE)</x:v>
+        <x:v>Nicardipine — entretien (IVSE)</x:v>
       </x:c>
       <x:c r="C51" s="3" t="str">
         <x:v>Loxen</x:v>
@@ -2096,7 +2143,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I51" s="3" t="str">
-        <x:v>Nicardipine</x:v>
+        <x:v>Nicardipine — entretien</x:v>
       </x:c>
       <x:c r="J51" s="3" t="str">
         <x:v>à confirmer</x:v>
@@ -2169,7 +2216,7 @@
         <x:v>Sufentanil</x:v>
       </x:c>
       <x:c r="J53" s="3" t="str">
-        <x:v>à confirmer</x:v>
+        <x:v>confirmé</x:v>
       </x:c>
       <x:c r="K53" s="3" t="str"/>
       <x:c r="L53" s="3" t="str">
@@ -2279,36 +2326,34 @@
         <x:v>calcium-gluconate</x:v>
       </x:c>
       <x:c r="B57" s="3" t="str">
-        <x:v>Gluconate Ca2+ 10 %</x:v>
+        <x:v>Gluconate de calcium 10 %</x:v>
       </x:c>
       <x:c r="C57" s="3" t="str">
-        <x:v>Gluconate de calcium PROAMP</x:v>
+        <x:v>Gluconate de calcium 10 %</x:v>
       </x:c>
       <x:c r="D57" s="7" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="E57" s="7" t="n">
-        <x:v>91</x:v>
-      </x:c>
+      <x:c r="E57" s="7"/>
       <x:c r="F57" s="6" t="str">
-        <x:v>mg</x:v>
-      </x:c>
-      <x:c r="G57" s="7"/>
+        <x:v>g</x:v>
+      </x:c>
+      <x:c r="G57" s="7" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
       <x:c r="H57" s="9" t="n">
         <x:f>IF(AND(ISNUMBER(D57),D57&gt;0,ISNUMBER(E57),E57&gt;0),E57/D57,IF(ISNUMBER(G57),G57,""))</x:f>
-        <x:v>9.1</x:v>
+        <x:v>0.1</x:v>
       </x:c>
       <x:c r="I57" s="3" t="str">
-        <x:v>calcium élément (PROAMP 10 %)</x:v>
+        <x:v>concentration nominale à 10 % ; prescription en mL de solution</x:v>
       </x:c>
       <x:c r="J57" s="3" t="str">
-        <x:v>à confirmer</x:v>
-      </x:c>
-      <x:c r="K57" s="3" t="str">
-        <x:v>La dose et la dilution restent à trancher indépendamment de l’ampoule.</x:v>
-      </x:c>
+        <x:v>confirmé</x:v>
+      </x:c>
+      <x:c r="K57" s="3" t="str"/>
       <x:c r="L57" s="3" t="str">
-        <x:v>https://base-donnees-publique.medicaments.gouv.fr/medicament/68332774/extrait</x:v>
+        <x:v>Tableau Prescription / Ampoules et décisions locales de la conversation</x:v>
       </x:c>
     </x:row>
     <x:row r="58" ht="58" customHeight="1">
@@ -2316,10 +2361,10 @@
         <x:v>insuline-glucose</x:v>
       </x:c>
       <x:c r="B58" s="3" t="str">
-        <x:v>Insuline rapide + G5 %</x:v>
+        <x:v>Insuline rapide + G10 %</x:v>
       </x:c>
       <x:c r="C58" s="3" t="str">
-        <x:v>Insuline rapide — spécialité à renseigner</x:v>
+        <x:v>Insuline rapide — concentration à renseigner</x:v>
       </x:c>
       <x:c r="D58" s="7"/>
       <x:c r="E58" s="7"/>
@@ -2337,7 +2382,7 @@
         <x:v>à confirmer</x:v>
       </x:c>
       <x:c r="K58" s="3" t="str">
-        <x:v>Préciser la spécialité et sa compatibilité avec G5 %. Le second produit est une poche de 500 mL de G5 % ; mélange local : 15 UI dans 500 mL.</x:v>
+        <x:v>G10 % : 5 mL/kg (max. 250 mL). Insuline : 0,1 UI/kg (max. 10 UI). Concentration d’insuline nécessaire pour son volume de prélèvement.</x:v>
       </x:c>
       <x:c r="L58" s="3" t="str">
         <x:v>Tableau Prescription / Ampoules et décisions locales de la conversation</x:v>
@@ -2521,21 +2566,132 @@
         <x:v>Tableau Prescription / Ampoules et décisions locales de la conversation</x:v>
       </x:c>
     </x:row>
+    <x:row r="65" ht="58" customHeight="1">
+      <x:c r="A65" s="18" t="str">
+        <x:v>triphosadenine-2</x:v>
+      </x:c>
+      <x:c r="B65" s="18" t="str">
+        <x:v>Triphosadénine — 2e dose</x:v>
+      </x:c>
+      <x:c r="C65" s="18" t="str">
+        <x:v>Triphosadénine</x:v>
+      </x:c>
+      <x:c r="D65" s="21" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E65" s="21" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="F65" s="19" t="str">
+        <x:v>mg</x:v>
+      </x:c>
+      <x:c r="G65" s="21"/>
+      <x:c r="H65" s="22" t="n">
+        <x:f>IF(AND(ISNUMBER(D65),D65&gt;0,ISNUMBER(E65),E65&gt;0),E65/D65,IF(ISNUMBER(G65),G65,""))</x:f>
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="I65" s="18" t="str">
+        <x:v>Triphosadénine — 2e dose</x:v>
+      </x:c>
+      <x:c r="J65" s="18" t="str">
+        <x:v>à confirmer</x:v>
+      </x:c>
+      <x:c r="K65" s="18" t="str"/>
+      <x:c r="L65" s="18" t="str">
+        <x:v>Tableau Prescription / Ampoules et décisions locales de la conversation</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="66" ht="58" customHeight="1">
+      <x:c r="A66" s="18" t="str">
+        <x:v>propofol-lisa</x:v>
+      </x:c>
+      <x:c r="B66" s="18" t="str">
+        <x:v>Propofol LISA</x:v>
+      </x:c>
+      <x:c r="C66" s="18" t="str">
+        <x:v>Propofol</x:v>
+      </x:c>
+      <x:c r="D66" s="21" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="E66" s="21" t="n">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="F66" s="19" t="str">
+        <x:v>mg</x:v>
+      </x:c>
+      <x:c r="G66" s="21"/>
+      <x:c r="H66" s="22" t="n">
+        <x:f>IF(AND(ISNUMBER(D66),D66&gt;0,ISNUMBER(E66),E66&gt;0),E66/D66,IF(ISNUMBER(G66),G66,""))</x:f>
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="I66" s="18" t="str">
+        <x:v>Propofol LISA</x:v>
+      </x:c>
+      <x:c r="J66" s="18" t="str">
+        <x:v>confirmé</x:v>
+      </x:c>
+      <x:c r="K66" s="18" t="str"/>
+      <x:c r="L66" s="18" t="str">
+        <x:v>Tableau Prescription / Ampoules et décisions locales de la conversation</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="67" ht="58" customHeight="1">
+      <x:c r="A67" s="18" t="str">
+        <x:v>nicardipine-charge</x:v>
+      </x:c>
+      <x:c r="B67" s="18" t="str">
+        <x:v>Nicardipine — dose de charge (IVSE)</x:v>
+      </x:c>
+      <x:c r="C67" s="18" t="str">
+        <x:v>Nicardipine</x:v>
+      </x:c>
+      <x:c r="D67" s="21" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E67" s="21" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F67" s="19" t="str">
+        <x:v>mg</x:v>
+      </x:c>
+      <x:c r="G67" s="21"/>
+      <x:c r="H67" s="22" t="n">
+        <x:f>IF(AND(ISNUMBER(D67),D67&gt;0,ISNUMBER(E67),E67&gt;0),E67/D67,IF(ISNUMBER(G67),G67,""))</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I67" s="18" t="str">
+        <x:v>Nicardipine — dose de charge</x:v>
+      </x:c>
+      <x:c r="J67" s="18" t="str">
+        <x:v>à confirmer</x:v>
+      </x:c>
+      <x:c r="K67" s="18" t="str"/>
+      <x:c r="L67" s="18" t="str">
+        <x:v>Tableau Prescription / Ampoules et décisions locales de la conversation</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="J2:J64">
     <x:cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="à confirmer"/>
   </x:conditionalFormatting>
-  <x:dataValidations count="2">
+  <x:dataValidations count="4">
     <x:dataValidation type="list" sqref="J2:J64">
       <x:formula1>"confirmé,à confirmer,sans objet"</x:formula1>
     </x:dataValidation>
     <x:dataValidation type="list" sqref="F2:F64">
       <x:formula1>"g,mg,mcg,ng,mmol,UI"</x:formula1>
     </x:dataValidation>
+    <x:dataValidation type="list" sqref="F2:F67">
+      <x:formula1>"g,mg,mcg,ng,mmol,UI"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="J2:J67">
+      <x:formula1>"confirmé,à confirmer,sans objet"</x:formula1>
+    </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc0165404d5804acf"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcf0ebf68c7c240a3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2553,7 +2709,7 @@
         <x:v>PediDoses — Tableau des ampoules</x:v>
       </x:c>
       <x:c r="B1" s="15" t="str">
-        <x:v>Version initiale : v0.6 — une ligne par fiche et par voie.</x:v>
+        <x:v>Version v0.9 — 66 lignes, une par fiche et par voie.</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="80" customHeight="1">
@@ -2625,7 +2781,7 @@
         <x:v>9. Sulfate de magnésium</x:v>
       </x:c>
       <x:c r="B10" s="3" t="str">
-        <x:v>Volume : 10 mL. Quantité totale laissée vide : la saisie « 0,15 g » doit être précisée (par mL ou par ampoule). Une solution à 15 % correspond à 1,5 g/10 mL. Dans l’application, aucun volume n’est calculé avant confirmation.</x:v>
+        <x:v>Sulfate de magnésium 15 % confirmé : 1,5 g dans 10 mL (150 mg/mL). Le volume à prélever est calculé ; la dilution finale reste à préciser.</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="80" customHeight="1">
@@ -2633,7 +2789,7 @@
         <x:v>10. Insuline et glucose</x:v>
       </x:c>
       <x:c r="B11" s="3" t="str">
-        <x:v>La ligne décrit l’insuline rapide à identifier. Le second produit est une poche de G5 % de 500 mL. Le mélange local demeure 15 UI dans 500 mL ; préciser la compatibilité de la spécialité avec G5 %.</x:v>
+        <x:v>Insuline rapide : 0,1 UI/kg, maximum 10 UI. G10 % : 5 mL/kg, maximum 250 mL. Administration sur 30 min. Les plafonds sont indépendants ; la concentration de l’insuline reste à renseigner pour calculer son prélèvement.</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="80" customHeight="1">
@@ -2641,7 +2797,7 @@
         <x:v>11. Triphosadénine</x:v>
       </x:c>
       <x:c r="B12" s="3" t="str">
-        <x:v>Posologie, préparation et administration laissées en suspens à la demande du prescripteur, faute d’informations. Aucun calcul automatique.</x:v>
+        <x:v>1re dose : 1 mg/kg, maximum 10 mg. 2e dose : 2 mg/kg, maximum 20 mg. Modalités IV à préciser.</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="80" customHeight="1">
